--- a/output/pdf_financials_xlsx/LIO.xlsx
+++ b/output/pdf_financials_xlsx/LIO.xlsx
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.377672</v>
+        <v>-0.377672</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8.507486</v>
+        <v>-8.507486</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>3.220692</v>
+        <v>-3.220692</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-2.261398</v>
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.377672</v>
+        <v>-0.377672</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>8.507486</v>
+        <v>-8.507486</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3.220692</v>
+        <v>-3.220692</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-2.261398</v>
@@ -1473,13 +1473,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.377672</v>
+        <v>-0.377672</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>8.507486</v>
+        <v>-8.507486</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>3.220692</v>
+        <v>-3.220692</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-2.261398</v>
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.377672</v>
+        <v>-0.377672</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>8.507486</v>
+        <v>-8.507486</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.220692</v>
+        <v>-3.220692</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-2.261398</v>
@@ -1769,13 +1769,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.377672</v>
+        <v>-0.377672</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>8.507486</v>
+        <v>-8.507486</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3.220692</v>
+        <v>-3.220692</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-2.261048</v>
@@ -1883,13 +1883,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -4827,34 +4827,34 @@
         <v>18.205973</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>18.441364</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>18.550075</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>18.83414</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>19.090965</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>21.203219</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>21.868222</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>22.846589</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>38.944699</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>41.359397</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>46.129964</v>
       </c>
     </row>
     <row r="93">
@@ -6016,22 +6016,22 @@
         <v>1.056115</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.6378200000000001</v>
+        <v>-5.536088</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.871851</v>
+        <v>-5.004752</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0.776136</v>
+        <v>-3.309673</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>3.122621</v>
+        <v>-34.433987</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0.755853</v>
+        <v>-4.483369</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0.210888</v>
+        <v>-1.539203</v>
       </c>
     </row>
     <row r="119">
@@ -8640,7 +8640,11 @@
           <t>Reserves (Note 16)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -10275,7 +10279,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -11415,7 +11423,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -14162,7 +14174,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -19546,7 +19562,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -36393,10 +36413,10 @@
         </is>
       </c>
       <c r="F371" s="5" t="n">
-        <v>7.891272</v>
+        <v>-7.891272</v>
       </c>
       <c r="G371" s="5" t="n">
-        <v>2.904648</v>
+        <v>-2.904648</v>
       </c>
       <c r="H371" s="5" t="n">
         <v>-2.33829</v>
@@ -37853,10 +37873,10 @@
         </is>
       </c>
       <c r="F389" s="5" t="n">
-        <v>8.507486</v>
+        <v>-8.507486</v>
       </c>
       <c r="G389" s="5" t="n">
-        <v>3.220692</v>
+        <v>-3.220692</v>
       </c>
       <c r="H389" t="inlineStr">
         <is>
@@ -38745,10 +38765,10 @@
         </is>
       </c>
       <c r="E400" s="5" t="n">
-        <v>0.377672</v>
+        <v>-0.377672</v>
       </c>
       <c r="F400" s="5" t="n">
-        <v>2.374083</v>
+        <v>-2.374083</v>
       </c>
       <c r="G400" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/LIO.xlsx
+++ b/output/pdf_financials_xlsx/LIO.xlsx
@@ -918,40 +918,40 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.090702</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.233956</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.182074</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.153401</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.07204099999999999</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.072798</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.380739</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.318571</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.265826</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>1.147124</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.900116</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.378843</v>
       </c>
     </row>
     <row r="13">
@@ -1680,40 +1680,40 @@
         <v>-0.377672</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-8.507486</v>
+        <v>-8.416784</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.220692</v>
+        <v>-2.986736</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.261398</v>
+        <v>-2.443472</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-5.227113</v>
+        <v>-5.380514</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.986485</v>
+        <v>-2.058526</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.360354</v>
+        <v>-2.433152</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.249517</v>
+        <v>-2.630256</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.221436</v>
+        <v>-2.540007</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.723822</v>
+        <v>-2.989648</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.909551</v>
+        <v>-4.056675</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-27.336738</v>
+        <v>-28.236854</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.715062</v>
+        <v>-3.093905</v>
       </c>
     </row>
     <row r="28">
@@ -1772,40 +1772,40 @@
         <v>-0.377672</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-8.507486</v>
+        <v>-8.416784</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.220692</v>
+        <v>-2.986736</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.261048</v>
+        <v>-2.443122</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.216597</v>
+        <v>-5.369998</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.981867</v>
+        <v>-2.053908</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.35933</v>
+        <v>-2.432128</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.249517</v>
+        <v>-2.630256</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.221436</v>
+        <v>-2.540007</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.568756</v>
+        <v>-2.834582</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.764943</v>
+        <v>-3.912067</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-27.223504</v>
+        <v>-28.12362</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.601828</v>
+        <v>-2.980671</v>
       </c>
     </row>
     <row r="30">
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-184.547536431245</v>
+        <v>-190.6494030499707</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-4.488373300983628</v>
+        <v>-5.141909509551043</v>
       </c>
     </row>
     <row r="31">
@@ -2013,19 +2013,19 @@
         <v>15.971997</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>13.576266</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>8.040357</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>4.144571</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.062154</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>19.574527</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>8.907418</v>
@@ -2040,7 +2040,7 @@
         <v>6.731873</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>5.102192</v>
       </c>
     </row>
     <row r="35">
@@ -2105,19 +2105,19 @@
         <v>15.971997</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>13.576266</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>8.040357</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>4.144571</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.062154</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>19.574527</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>8.907418</v>
@@ -2132,7 +2132,7 @@
         <v>6.731873</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>5.102192</v>
       </c>
     </row>
     <row r="37">
@@ -2657,19 +2657,19 @@
         <v>0.476767</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>13.608876</v>
+        <v>0.03261</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>8.076250999999999</v>
+        <v>0.035894</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>4.157186</v>
+        <v>0.012615</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.072656</v>
+        <v>0.010502</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>19.654595</v>
+        <v>0.080068</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.06279</v>
@@ -2684,7 +2684,7 @@
         <v>0.6262450000000001</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>7.393833</v>
+        <v>2.291641</v>
       </c>
     </row>
     <row r="49">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -31855,7 +31855,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -33145,7 +33145,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -33962,7 +33962,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -37781,7 +37781,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">

--- a/output/pdf_financials_xlsx/LIO.xlsx
+++ b/output/pdf_financials_xlsx/LIO.xlsx
@@ -695,22 +695,22 @@
         <v>1.372695</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.283366</v>
+        <v>1.297491</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1.260995</v>
+        <v>1.284995</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.011054</v>
+        <v>1.031054</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.47185</v>
+        <v>1.49485</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.399976</v>
+        <v>1.422976</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.479354</v>
+        <v>1.499437</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>0</v>
@@ -842,13 +842,13 @@
         <v>0.69885</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.47185</v>
+        <v>1.49485</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1.399976</v>
+        <v>1.422976</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.479354</v>
+        <v>1.499437</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>4.746831</v>
@@ -5673,13 +5673,13 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00494</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.120812</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.603111</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>-0.139021</v>
@@ -6775,13 +6775,13 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00494</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.120812</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.603111</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>-0.139021</v>
@@ -14494,7 +14494,11 @@
           <t>Cash proceeds from sale of shares – private placement</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -14569,7 +14573,11 @@
           <t>Share issuance costs on private placement</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -15726,7 +15734,11 @@
           <t>Value of warrants issued in private placement</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -17972,7 +17984,11 @@
           <t>Value of warrants issued in private placement</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -18855,7 +18871,11 @@
           <t>Private placement 24,150,000</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -25093,7 +25113,11 @@
           <t>Issuance of shares from private placement</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -25490,7 +25514,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E235" s="5" t="n">
         <v>-0.00494</v>
       </c>
@@ -27254,7 +27282,11 @@
           <t>Issuance of shares on private placement</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -32989,7 +33021,11 @@
           <t>Directors’ fees (Note 9)</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -35831,7 +35867,11 @@
           <t>Directors’ fees (Note 11)</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E364" t="inlineStr">
         <is>
           <t>-</t>
